--- a/astro-site/public/dl/guia-panaderia-obrador/calculadora-ticket-medio.xlsx
+++ b/astro-site/public/dl/guia-panaderia-obrador/calculadora-ticket-medio.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ticket Medio" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Ticket Medio'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -448,7 +450,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -467,6 +469,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -508,7 +511,7 @@
       </c>
       <c r="D4">
         <f>B4*C4/100</f>
-        <v/>
+        <v>0.48400000000000004</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -530,9 +533,8 @@
       </c>
       <c r="D5">
         <f>B5*C5/100</f>
-        <v/>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>0.49</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -548,7 +550,7 @@
       </c>
       <c r="D6">
         <f>B6*C6/100</f>
-        <v/>
+        <v>0.7440000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -570,7 +572,7 @@
       </c>
       <c r="D7">
         <f>B7*C7/100</f>
-        <v/>
+        <v>0.675</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -592,9 +594,8 @@
       </c>
       <c r="D8">
         <f>B8*C8/100</f>
-        <v/>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>0.27</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -610,7 +611,7 @@
       </c>
       <c r="D9">
         <f>B9*C9/100</f>
-        <v/>
+        <v>0.28</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -632,7 +633,7 @@
       </c>
       <c r="D10">
         <f>B10*C10/100</f>
-        <v/>
+        <v>0.24200000000000002</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -654,9 +655,8 @@
       </c>
       <c r="D11">
         <f>B11*C11/100</f>
-        <v/>
-      </c>
-      <c r="E11" t="inlineStr"/>
+        <v>0.20800000000000002</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -672,9 +672,8 @@
       </c>
       <c r="D12">
         <f>B12*C12/100</f>
-        <v/>
-      </c>
-      <c r="E12" t="inlineStr"/>
+        <v>0.13299999999999998</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -690,9 +689,8 @@
       </c>
       <c r="D13">
         <f>B13*C13/100</f>
-        <v/>
-      </c>
-      <c r="E13" t="inlineStr"/>
+        <v>0.11199999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -708,7 +706,7 @@
       </c>
       <c r="D14">
         <f>B14*C14/100</f>
-        <v/>
+        <v>0.10800000000000001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -730,31 +728,23 @@
       </c>
       <c r="D15">
         <f>B15*C15/100</f>
-        <v/>
-      </c>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
           <t>TICKET MEDIO PROYECTADO</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17">
         <f>SUM(C4:C15)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D17">
         <f>SUM(D4:D15)</f>
-        <v/>
+        <v>3.766</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -766,6 +756,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>